--- a/assets/competences.xlsx
+++ b/assets/competences.xlsx
@@ -5,10 +5,10 @@
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\bobom\Desktop\portofio\assets\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\bobom\Downloads\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{5B0C5D0C-BEDF-46D3-B98C-DC176D3C6038}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D884A3C6-965C-47E2-8261-B9FFD6A25725}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -20,18 +20,18 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="138" uniqueCount="62">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="165" uniqueCount="66">
   <si>
     <t>BTS SERVICES INFORMATIQUES AUX ORGANISATIONS</t>
   </si>
   <si>
-    <t>SESSION 2025</t>
+    <t>SESSION 2026</t>
   </si>
   <si>
     <t xml:space="preserve">Tableau de synthèse des réalisations professionnelles </t>
   </si>
   <si>
-    <t>NOM et prénom : Lachkar Bilal</t>
+    <t>NOM et prénom : Mzili Adam</t>
   </si>
   <si>
     <t xml:space="preserve">N° candidat : </t>
@@ -47,6 +47,9 @@
   </si>
   <si>
     <t>▢ SLAM</t>
+  </si>
+  <si>
+    <t>Adresse URL du portfolio : https://fiocko.github.io/</t>
   </si>
   <si>
     <t>Compétences mises en œuvre
@@ -131,10 +134,13 @@
     <t>Configuration réseau et adressage IP (VLAN, sous-réseaux)</t>
   </si>
   <si>
-    <t>01/2025 au 05/2025</t>
+    <t>01/2025 au 05/2026</t>
   </si>
   <si>
     <t>Sécurisation d'un serveur Web Apache sous Debian</t>
+  </si>
+  <si>
+    <t>01/2025 au 05/2025</t>
   </si>
   <si>
     <t>Création de Machines Virtuelles Debian, Ubuntu (VirtualBox)</t>
@@ -149,10 +155,7 @@
     <t>09/2024 au 06/2025</t>
   </si>
   <si>
-    <t>Mise en place d'un serveur DHCP/DNS sous Linux</t>
-  </si>
-  <si>
-    <t>01/2025 au 05/2026</t>
+    <t>Mise en place d'un serveur DHCP/DNS sous Windows</t>
   </si>
   <si>
     <t>Déploiement d'Active Directory et gestion des GPO (Windows Server)</t>
@@ -164,7 +167,13 @@
     <t>Scripting d'automatisation Bash et PowerShell</t>
   </si>
   <si>
-    <t>09/2025 au 05/2026</t>
+    <t>09/2024 au 05/2025</t>
+  </si>
+  <si>
+    <t>Cybersécurité : certificats numériques HTTPS et chiffrement OpenSSL</t>
+  </si>
+  <si>
+    <t>Gestion du stockage : RAID, partages et permissions NTFS (Windows Server)</t>
   </si>
   <si>
     <t>Portfolio professionnel</t>
@@ -176,7 +185,7 @@
     <t>Réalisations en milieu professionnel en cours de première année</t>
   </si>
   <si>
-    <t>Inventaire et mise à jour du parc informatique (GLPI)</t>
+    <t>Recensement du parc informatique (gestionnaire DNS)</t>
   </si>
   <si>
     <t>19/05/25 au 20/06/25</t>
@@ -197,41 +206,44 @@
     <t>Création et gestion des comptes utilisateurs (Active Directory)</t>
   </si>
   <si>
+    <t>19/05/25 au 13/06/25</t>
+  </si>
+  <si>
     <t>Rédaction de documentation technique et procédures</t>
   </si>
   <si>
     <t>Réalisations en milieu professionnel en cours de seconde année</t>
   </si>
   <si>
-    <t>Administration de serveurs Windows Server (rôles, services)</t>
+    <t>Mise en place et configuration de GLPI (système de tickets)</t>
   </si>
   <si>
     <t>15/12/25 au 06/02/26</t>
   </si>
   <si>
-    <t>Déploiement d'une solution de virtualisation (VMware/VirtualBox)</t>
+    <t>Déploiement et configuration de nouveaux postes Windows 11</t>
   </si>
   <si>
-    <t>Supervision et monitoring réseau (Zabbix / PRTG)</t>
+    <t>Maintenance préventive et corrective du parc informatique</t>
   </si>
   <si>
-    <t>Sécurisation du réseau : pare-feu, VPN, ACL</t>
+    <t>Sécurisation des accès réseau et gestion des droits utilisateurs</t>
   </si>
   <si>
-    <t>Gestion et vérification des sauvegardes (Veeam/Bacula)</t>
+    <t>Vérification et test du plan de sauvegarde des données</t>
   </si>
   <si>
-    <t>Rédaction de procédures et rapports d'intervention</t>
+    <t>Rédaction de fiches d'intervention et de procédures techniques</t>
   </si>
   <si>
-    <t>Adresse URL du portfolio : https://fiocko.github.io/</t>
+    <t>Gestion et mise à jour du site web de l'association</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="14" x14ac:knownFonts="1">
+  <fonts count="15" x14ac:knownFonts="1">
     <font>
       <sz val="10"/>
       <color rgb="FF000000"/>
@@ -304,18 +316,26 @@
       <name val="Arial"/>
     </font>
     <font>
-      <sz val="11"/>
-      <color theme="1"/>
-      <name val="Arial"/>
-    </font>
-    <font>
       <b/>
       <sz val="10"/>
       <color rgb="FF000000"/>
       <name val="Arial"/>
     </font>
+    <font>
+      <sz val="10"/>
+      <color theme="1"/>
+      <name val="Arial"/>
+      <family val="2"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="18"/>
+      <color theme="1"/>
+      <name val="Arial"/>
+      <family val="2"/>
+    </font>
   </fonts>
-  <fills count="4">
+  <fills count="5">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -332,6 +352,12 @@
       <patternFill patternType="solid">
         <fgColor rgb="FFFFFFFF"/>
         <bgColor rgb="FFFFFFFF"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="0"/>
+        <bgColor rgb="FF93C47D"/>
       </patternFill>
     </fill>
   </fills>
@@ -701,7 +727,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="48">
+  <cellXfs count="47">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
@@ -734,7 +760,6 @@
     <xf numFmtId="0" fontId="9" fillId="0" borderId="18" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="2" borderId="19" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="10" fillId="0" borderId="18" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
@@ -744,16 +769,11 @@
     <xf numFmtId="0" fontId="9" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="3" borderId="19" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="10" fillId="3" borderId="19" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="1" fontId="11" fillId="3" borderId="20" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="3" borderId="19" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="10" fillId="3" borderId="19" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="11" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
@@ -761,19 +781,30 @@
     <xf numFmtId="0" fontId="10" fillId="3" borderId="21" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="10" fillId="3" borderId="18" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
+    <xf numFmtId="0" fontId="4" fillId="2" borderId="19" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment vertical="center"/>
+    <xf numFmtId="0" fontId="13" fillId="2" borderId="19" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="4" fillId="3" borderId="19" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="4" borderId="19" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="24" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="4" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="7" xfId="0" applyBorder="1"/>
+    <xf numFmtId="1" fontId="12" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="17" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
@@ -785,10 +816,6 @@
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="24" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="7" xfId="0" applyBorder="1"/>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="26" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
@@ -810,7 +837,7 @@
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="13" xfId="0" applyBorder="1"/>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="25" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="25" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyBorder="1"/>
@@ -1032,7 +1059,7 @@
   <sheetPr>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:M1001"/>
+  <dimension ref="A1:M1003"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="12.5703125" defaultRowHeight="15" customHeight="1" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="70.42578125" customWidth="1"/>
@@ -1042,18 +1069,18 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:13" ht="39.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A1" s="31" t="s">
+      <c r="A1" s="32" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="32"/>
-      <c r="C1" s="32"/>
-      <c r="D1" s="32"/>
-      <c r="E1" s="32"/>
-      <c r="F1" s="32"/>
-      <c r="G1" s="31" t="s">
+      <c r="B1" s="33"/>
+      <c r="C1" s="33"/>
+      <c r="D1" s="33"/>
+      <c r="E1" s="33"/>
+      <c r="F1" s="33"/>
+      <c r="G1" s="32" t="s">
         <v>1</v>
       </c>
-      <c r="H1" s="32"/>
+      <c r="H1" s="33"/>
       <c r="I1" s="1"/>
       <c r="J1" s="1"/>
       <c r="K1" s="1"/>
@@ -1061,16 +1088,16 @@
       <c r="M1" s="1"/>
     </row>
     <row r="2" spans="1:13" ht="40.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A2" s="31" t="s">
+      <c r="A2" s="32" t="s">
         <v>2</v>
       </c>
-      <c r="B2" s="32"/>
-      <c r="C2" s="32"/>
-      <c r="D2" s="32"/>
-      <c r="E2" s="32"/>
-      <c r="F2" s="32"/>
-      <c r="G2" s="32"/>
-      <c r="H2" s="32"/>
+      <c r="B2" s="33"/>
+      <c r="C2" s="33"/>
+      <c r="D2" s="33"/>
+      <c r="E2" s="33"/>
+      <c r="F2" s="33"/>
+      <c r="G2" s="33"/>
+      <c r="H2" s="33"/>
       <c r="I2" s="1"/>
       <c r="J2" s="1"/>
       <c r="K2" s="1"/>
@@ -1078,18 +1105,18 @@
       <c r="M2" s="1"/>
     </row>
     <row r="3" spans="1:13" ht="39.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A3" s="46" t="s">
+      <c r="A3" s="45" t="s">
         <v>3</v>
       </c>
-      <c r="B3" s="39"/>
-      <c r="C3" s="39"/>
-      <c r="D3" s="39"/>
-      <c r="E3" s="47"/>
-      <c r="F3" s="38" t="s">
+      <c r="B3" s="38"/>
+      <c r="C3" s="38"/>
+      <c r="D3" s="38"/>
+      <c r="E3" s="46"/>
+      <c r="F3" s="37" t="s">
         <v>4</v>
       </c>
-      <c r="G3" s="39"/>
-      <c r="H3" s="40"/>
+      <c r="G3" s="38"/>
+      <c r="H3" s="39"/>
       <c r="I3" s="1"/>
       <c r="J3" s="1"/>
       <c r="K3" s="2"/>
@@ -1097,13 +1124,13 @@
       <c r="M3" s="2"/>
     </row>
     <row r="4" spans="1:13" ht="39.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A4" s="28" t="s">
+      <c r="A4" s="29" t="s">
         <v>5</v>
       </c>
-      <c r="B4" s="29"/>
-      <c r="C4" s="29"/>
-      <c r="D4" s="29"/>
-      <c r="E4" s="30"/>
+      <c r="B4" s="30"/>
+      <c r="C4" s="30"/>
+      <c r="D4" s="30"/>
+      <c r="E4" s="31"/>
       <c r="F4" s="3" t="s">
         <v>6</v>
       </c>
@@ -1120,16 +1147,16 @@
       <c r="M4" s="1"/>
     </row>
     <row r="5" spans="1:13" ht="39.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A5" s="35" t="s">
-        <v>61</v>
+      <c r="A5" s="34" t="s">
+        <v>9</v>
       </c>
-      <c r="B5" s="36"/>
-      <c r="C5" s="36"/>
-      <c r="D5" s="36"/>
-      <c r="E5" s="36"/>
-      <c r="F5" s="36"/>
-      <c r="G5" s="36"/>
-      <c r="H5" s="37"/>
+      <c r="B5" s="35"/>
+      <c r="C5" s="35"/>
+      <c r="D5" s="35"/>
+      <c r="E5" s="35"/>
+      <c r="F5" s="35"/>
+      <c r="G5" s="35"/>
+      <c r="H5" s="36"/>
       <c r="I5" s="1"/>
       <c r="J5" s="1"/>
       <c r="K5" s="1"/>
@@ -1137,29 +1164,29 @@
       <c r="M5" s="1"/>
     </row>
     <row r="6" spans="1:13" ht="90" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A6" s="44" t="s">
-        <v>9</v>
-      </c>
-      <c r="B6" s="41" t="s">
+      <c r="A6" s="43" t="s">
         <v>10</v>
       </c>
-      <c r="C6" s="6" t="s">
+      <c r="B6" s="40" t="s">
         <v>11</v>
       </c>
-      <c r="D6" s="6" t="s">
+      <c r="C6" s="6" t="s">
         <v>12</v>
       </c>
-      <c r="E6" s="6" t="s">
+      <c r="D6" s="6" t="s">
         <v>13</v>
       </c>
-      <c r="F6" s="6" t="s">
+      <c r="E6" s="6" t="s">
         <v>14</v>
       </c>
-      <c r="G6" s="6" t="s">
+      <c r="F6" s="6" t="s">
         <v>15</v>
       </c>
+      <c r="G6" s="6" t="s">
+        <v>16</v>
+      </c>
       <c r="H6" s="7" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="I6" s="1"/>
       <c r="J6" s="1"/>
@@ -1168,25 +1195,25 @@
       <c r="M6" s="1"/>
     </row>
     <row r="7" spans="1:13" ht="324.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A7" s="45"/>
-      <c r="B7" s="42"/>
+      <c r="A7" s="44"/>
+      <c r="B7" s="41"/>
       <c r="C7" s="8" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="D7" s="8" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="E7" s="8" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="F7" s="8" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="G7" s="8" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="H7" s="9" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="I7" s="1"/>
       <c r="J7" s="1"/>
@@ -1195,16 +1222,16 @@
       <c r="M7" s="1"/>
     </row>
     <row r="8" spans="1:13" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A8" s="43" t="s">
-        <v>23</v>
+      <c r="A8" s="42" t="s">
+        <v>24</v>
       </c>
-      <c r="B8" s="39"/>
-      <c r="C8" s="39"/>
-      <c r="D8" s="39"/>
-      <c r="E8" s="39"/>
-      <c r="F8" s="39"/>
-      <c r="G8" s="39"/>
-      <c r="H8" s="40"/>
+      <c r="B8" s="38"/>
+      <c r="C8" s="38"/>
+      <c r="D8" s="38"/>
+      <c r="E8" s="38"/>
+      <c r="F8" s="38"/>
+      <c r="G8" s="38"/>
+      <c r="H8" s="39"/>
       <c r="I8" s="1"/>
       <c r="J8" s="1"/>
       <c r="K8" s="1"/>
@@ -1213,20 +1240,20 @@
     </row>
     <row r="9" spans="1:13" ht="39.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A9" s="10" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="B9" s="11" t="s">
-        <v>25</v>
-      </c>
-      <c r="C9" s="12" t="s">
         <v>26</v>
       </c>
-      <c r="D9" s="13"/>
-      <c r="E9" s="13"/>
-      <c r="F9" s="13"/>
-      <c r="G9" s="13"/>
-      <c r="H9" s="12" t="s">
-        <v>26</v>
+      <c r="C9" s="21" t="s">
+        <v>27</v>
+      </c>
+      <c r="D9" s="12"/>
+      <c r="E9" s="12"/>
+      <c r="F9" s="12"/>
+      <c r="G9" s="12"/>
+      <c r="H9" s="22" t="s">
+        <v>27</v>
       </c>
       <c r="I9" s="1"/>
       <c r="J9" s="1"/>
@@ -1236,24 +1263,24 @@
     </row>
     <row r="10" spans="1:13" ht="39.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A10" s="10" t="s">
+        <v>28</v>
+      </c>
+      <c r="B10" s="11" t="s">
+        <v>29</v>
+      </c>
+      <c r="C10" s="21" t="s">
         <v>27</v>
       </c>
-      <c r="B10" s="11" t="s">
-        <v>28</v>
+      <c r="D10" s="21" t="s">
+        <v>27</v>
       </c>
-      <c r="C10" s="12" t="s">
-        <v>26</v>
+      <c r="E10" s="12"/>
+      <c r="F10" s="12"/>
+      <c r="G10" s="21" t="s">
+        <v>27</v>
       </c>
-      <c r="D10" s="12" t="s">
-        <v>26</v>
-      </c>
-      <c r="E10" s="13"/>
-      <c r="F10" s="13"/>
-      <c r="G10" s="13" t="s">
-        <v>26</v>
-      </c>
-      <c r="H10" s="12" t="s">
-        <v>26</v>
+      <c r="H10" s="21" t="s">
+        <v>27</v>
       </c>
       <c r="I10" s="1"/>
       <c r="J10" s="1"/>
@@ -1263,24 +1290,24 @@
     </row>
     <row r="11" spans="1:13" ht="39.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A11" s="10" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="B11" s="11" t="s">
-        <v>30</v>
+        <v>31</v>
       </c>
-      <c r="C11" s="12" t="s">
-        <v>26</v>
+      <c r="C11" s="21" t="s">
+        <v>27</v>
       </c>
-      <c r="D11" s="13"/>
-      <c r="E11" s="13"/>
-      <c r="F11" s="13" t="s">
-        <v>26</v>
+      <c r="D11" s="12"/>
+      <c r="E11" s="12"/>
+      <c r="F11" s="22" t="s">
+        <v>27</v>
       </c>
-      <c r="G11" s="13" t="s">
-        <v>26</v>
+      <c r="G11" s="22" t="s">
+        <v>27</v>
       </c>
-      <c r="H11" s="12" t="s">
-        <v>26</v>
+      <c r="H11" s="21" t="s">
+        <v>27</v>
       </c>
       <c r="I11" s="1"/>
       <c r="J11" s="1"/>
@@ -1290,22 +1317,22 @@
     </row>
     <row r="12" spans="1:13" ht="39.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A12" s="10" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="B12" s="11" t="s">
-        <v>30</v>
+        <v>33</v>
       </c>
-      <c r="C12" s="12" t="s">
-        <v>26</v>
+      <c r="C12" s="21" t="s">
+        <v>27</v>
       </c>
-      <c r="D12" s="13"/>
-      <c r="E12" s="13"/>
-      <c r="F12" s="13"/>
-      <c r="G12" s="13" t="s">
-        <v>26</v>
+      <c r="D12" s="12"/>
+      <c r="E12" s="12"/>
+      <c r="F12" s="12"/>
+      <c r="G12" s="22" t="s">
+        <v>27</v>
       </c>
-      <c r="H12" s="12" t="s">
-        <v>26</v>
+      <c r="H12" s="21" t="s">
+        <v>27</v>
       </c>
       <c r="I12" s="1"/>
       <c r="J12" s="1"/>
@@ -1315,22 +1342,22 @@
     </row>
     <row r="13" spans="1:13" ht="39.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A13" s="10" t="s">
-        <v>32</v>
+        <v>34</v>
       </c>
       <c r="B13" s="11" t="s">
-        <v>33</v>
+        <v>35</v>
       </c>
-      <c r="C13" s="12" t="s">
-        <v>26</v>
+      <c r="C13" s="21" t="s">
+        <v>27</v>
       </c>
-      <c r="D13" s="13"/>
-      <c r="E13" s="13"/>
-      <c r="F13" s="13"/>
-      <c r="G13" s="13" t="s">
-        <v>26</v>
+      <c r="D13" s="12"/>
+      <c r="E13" s="12"/>
+      <c r="F13" s="12"/>
+      <c r="G13" s="22" t="s">
+        <v>27</v>
       </c>
-      <c r="H13" s="12" t="s">
-        <v>26</v>
+      <c r="H13" s="21" t="s">
+        <v>27</v>
       </c>
       <c r="I13" s="1"/>
       <c r="J13" s="1"/>
@@ -1340,24 +1367,24 @@
     </row>
     <row r="14" spans="1:13" ht="39.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A14" s="10" t="s">
-        <v>34</v>
+        <v>36</v>
       </c>
       <c r="B14" s="11" t="s">
-        <v>35</v>
+        <v>37</v>
       </c>
-      <c r="C14" s="12" t="s">
-        <v>26</v>
+      <c r="C14" s="21" t="s">
+        <v>27</v>
       </c>
-      <c r="D14" s="13"/>
-      <c r="E14" s="13"/>
-      <c r="F14" s="13" t="s">
-        <v>26</v>
+      <c r="D14" s="12"/>
+      <c r="E14" s="12"/>
+      <c r="F14" s="22" t="s">
+        <v>27</v>
       </c>
-      <c r="G14" s="12" t="s">
-        <v>26</v>
+      <c r="G14" s="21" t="s">
+        <v>27</v>
       </c>
-      <c r="H14" s="12" t="s">
-        <v>26</v>
+      <c r="H14" s="21" t="s">
+        <v>27</v>
       </c>
       <c r="I14" s="1"/>
       <c r="J14" s="1"/>
@@ -1367,22 +1394,22 @@
     </row>
     <row r="15" spans="1:13" ht="39.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A15" s="10" t="s">
-        <v>36</v>
+        <v>38</v>
       </c>
       <c r="B15" s="11" t="s">
-        <v>37</v>
+        <v>31</v>
       </c>
-      <c r="C15" s="12" t="s">
-        <v>26</v>
+      <c r="C15" s="21" t="s">
+        <v>27</v>
       </c>
-      <c r="D15" s="13"/>
-      <c r="E15" s="13"/>
-      <c r="F15" s="13"/>
-      <c r="G15" s="13" t="s">
-        <v>26</v>
+      <c r="D15" s="12"/>
+      <c r="E15" s="12"/>
+      <c r="F15" s="12"/>
+      <c r="G15" s="22" t="s">
+        <v>27</v>
       </c>
-      <c r="H15" s="12" t="s">
-        <v>26</v>
+      <c r="H15" s="21" t="s">
+        <v>27</v>
       </c>
       <c r="I15" s="1"/>
       <c r="J15" s="1"/>
@@ -1392,26 +1419,26 @@
     </row>
     <row r="16" spans="1:13" ht="39.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A16" s="10" t="s">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="B16" s="11" t="s">
-        <v>39</v>
+        <v>40</v>
       </c>
-      <c r="C16" s="12" t="s">
-        <v>26</v>
+      <c r="C16" s="21" t="s">
+        <v>27</v>
       </c>
-      <c r="D16" s="12" t="s">
-        <v>26</v>
+      <c r="D16" s="21" t="s">
+        <v>27</v>
       </c>
-      <c r="E16" s="13"/>
-      <c r="F16" s="12" t="s">
-        <v>26</v>
+      <c r="E16" s="12"/>
+      <c r="F16" s="21" t="s">
+        <v>27</v>
       </c>
-      <c r="G16" s="12" t="s">
-        <v>26</v>
+      <c r="G16" s="21" t="s">
+        <v>27</v>
       </c>
-      <c r="H16" s="12" t="s">
-        <v>26</v>
+      <c r="H16" s="21" t="s">
+        <v>27</v>
       </c>
       <c r="I16" s="1"/>
       <c r="J16" s="1"/>
@@ -1421,22 +1448,22 @@
     </row>
     <row r="17" spans="1:13" ht="39.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A17" s="10" t="s">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="B17" s="11" t="s">
-        <v>41</v>
+        <v>42</v>
       </c>
-      <c r="C17" s="12" t="s">
-        <v>26</v>
+      <c r="C17" s="21" t="s">
+        <v>27</v>
       </c>
-      <c r="D17" s="13"/>
-      <c r="E17" s="13"/>
-      <c r="F17" s="13"/>
-      <c r="G17" s="12" t="s">
-        <v>26</v>
+      <c r="D17" s="12"/>
+      <c r="E17" s="12"/>
+      <c r="F17" s="12"/>
+      <c r="G17" s="21" t="s">
+        <v>27</v>
       </c>
-      <c r="H17" s="12" t="s">
-        <v>26</v>
+      <c r="H17" s="21" t="s">
+        <v>27</v>
       </c>
       <c r="I17" s="1"/>
       <c r="J17" s="1"/>
@@ -1446,86 +1473,82 @@
     </row>
     <row r="18" spans="1:13" ht="39.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A18" s="10" t="s">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="B18" s="11" t="s">
-        <v>43</v>
+        <v>31</v>
       </c>
-      <c r="C18" s="12" t="s">
-        <v>26</v>
+      <c r="C18" s="21" t="s">
+        <v>27</v>
       </c>
-      <c r="D18" s="13"/>
-      <c r="E18" s="13"/>
-      <c r="F18" s="13"/>
-      <c r="G18" s="12" t="s">
-        <v>26</v>
+      <c r="D18" s="12"/>
+      <c r="E18" s="12"/>
+      <c r="F18" s="12"/>
+      <c r="G18" s="21" t="s">
+        <v>27</v>
       </c>
-      <c r="H18" s="12" t="s">
-        <v>26</v>
+      <c r="H18" s="21" t="s">
+        <v>27</v>
       </c>
-      <c r="I18" s="1"/>
-      <c r="J18" s="1"/>
-      <c r="K18" s="1"/>
-      <c r="L18" s="1"/>
-      <c r="M18" s="1"/>
-    </row>
-    <row r="19" spans="1:13" ht="23.25" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A19" s="33" t="s">
+    </row>
+    <row r="19" spans="1:13" ht="39.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A19" s="10" t="s">
         <v>44</v>
       </c>
-      <c r="B19" s="29"/>
-      <c r="C19" s="29"/>
-      <c r="D19" s="29"/>
-      <c r="E19" s="29"/>
-      <c r="F19" s="29"/>
-      <c r="G19" s="29"/>
-      <c r="H19" s="34"/>
-      <c r="I19" s="1"/>
-      <c r="J19" s="1"/>
-      <c r="K19" s="1"/>
-      <c r="L19" s="1"/>
-      <c r="M19" s="1"/>
-    </row>
-    <row r="20" spans="1:13" ht="39.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A20" s="14" t="s">
+      <c r="B19" s="11" t="s">
+        <v>31</v>
+      </c>
+      <c r="C19" s="21" t="s">
+        <v>27</v>
+      </c>
+      <c r="D19" s="12"/>
+      <c r="E19" s="12"/>
+      <c r="F19" s="12"/>
+      <c r="G19" s="21" t="s">
+        <v>27</v>
+      </c>
+      <c r="H19" s="21" t="s">
+        <v>27</v>
+      </c>
+    </row>
+    <row r="20" spans="1:13" ht="39.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A20" s="10" t="s">
         <v>45</v>
       </c>
-      <c r="B20" s="15" t="s">
+      <c r="B20" s="11" t="s">
         <v>46</v>
       </c>
-      <c r="C20" s="12" t="s">
-        <v>26</v>
+      <c r="C20" s="21" t="s">
+        <v>27</v>
       </c>
-      <c r="D20" s="16" t="s">
-        <v>26</v>
+      <c r="D20" s="12"/>
+      <c r="E20" s="21" t="s">
+        <v>27</v>
       </c>
-      <c r="E20" s="17"/>
-      <c r="F20" s="16"/>
-      <c r="G20" s="16"/>
-      <c r="H20" s="17"/>
+      <c r="F20" s="12"/>
+      <c r="G20" s="21" t="s">
+        <v>27</v>
+      </c>
+      <c r="H20" s="21" t="s">
+        <v>27</v>
+      </c>
       <c r="I20" s="1"/>
       <c r="J20" s="1"/>
       <c r="K20" s="1"/>
       <c r="L20" s="1"/>
       <c r="M20" s="1"/>
     </row>
-    <row r="21" spans="1:13" ht="39.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A21" s="14" t="s">
+    <row r="21" spans="1:13" ht="39.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A21" s="25" t="s">
         <v>47</v>
       </c>
-      <c r="B21" s="15" t="s">
-        <v>46</v>
-      </c>
-      <c r="C21" s="12"/>
-      <c r="D21" s="16" t="s">
-        <v>26</v>
-      </c>
-      <c r="E21" s="16"/>
-      <c r="F21" s="16"/>
-      <c r="G21" s="16"/>
-      <c r="H21" s="12" t="s">
-        <v>26</v>
-      </c>
+      <c r="B21" s="26"/>
+      <c r="C21" s="26"/>
+      <c r="D21" s="26"/>
+      <c r="E21" s="26"/>
+      <c r="F21" s="26"/>
+      <c r="G21" s="26"/>
+      <c r="H21" s="27"/>
       <c r="I21" s="1"/>
       <c r="J21" s="1"/>
       <c r="K21" s="1"/>
@@ -1533,46 +1556,44 @@
       <c r="M21" s="1"/>
     </row>
     <row r="22" spans="1:13" ht="39.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A22" s="14" t="s">
+      <c r="A22" s="13" t="s">
         <v>48</v>
       </c>
-      <c r="B22" s="15" t="s">
-        <v>46</v>
+      <c r="B22" s="14" t="s">
+        <v>49</v>
       </c>
-      <c r="C22" s="12" t="s">
-        <v>26</v>
+      <c r="C22" s="21" t="s">
+        <v>27</v>
       </c>
-      <c r="D22" s="16"/>
-      <c r="E22" s="16"/>
-      <c r="F22" s="16"/>
-      <c r="G22" s="17" t="s">
-        <v>26</v>
+      <c r="D22" s="22" t="s">
+        <v>27</v>
       </c>
-      <c r="H22" s="17"/>
+      <c r="E22" s="15"/>
+      <c r="F22" s="23"/>
+      <c r="G22" s="23"/>
+      <c r="H22" s="15"/>
       <c r="I22" s="1"/>
       <c r="J22" s="1"/>
       <c r="K22" s="1"/>
       <c r="L22" s="1"/>
       <c r="M22" s="1"/>
     </row>
-    <row r="23" spans="1:13" ht="39.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A23" s="18" t="s">
+    <row r="23" spans="1:13" ht="39.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A23" s="13" t="s">
+        <v>50</v>
+      </c>
+      <c r="B23" s="14" t="s">
         <v>49</v>
       </c>
-      <c r="B23" s="15" t="s">
-        <v>46</v>
+      <c r="C23" s="24"/>
+      <c r="D23" s="22" t="s">
+        <v>27</v>
       </c>
-      <c r="C23" s="12" t="s">
-        <v>26</v>
-      </c>
-      <c r="D23" s="17"/>
-      <c r="E23" s="17"/>
-      <c r="F23" s="16"/>
-      <c r="G23" s="17" t="s">
-        <v>26</v>
-      </c>
-      <c r="H23" s="17" t="s">
-        <v>26</v>
+      <c r="E23" s="23"/>
+      <c r="F23" s="23"/>
+      <c r="G23" s="23"/>
+      <c r="H23" s="21" t="s">
+        <v>27</v>
       </c>
       <c r="I23" s="1"/>
       <c r="J23" s="1"/>
@@ -1580,23 +1601,23 @@
       <c r="L23" s="1"/>
       <c r="M23" s="1"/>
     </row>
-    <row r="24" spans="1:13" ht="39.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A24" s="18" t="s">
-        <v>50</v>
+    <row r="24" spans="1:13" ht="39.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A24" s="13" t="s">
+        <v>51</v>
       </c>
-      <c r="B24" s="15" t="s">
-        <v>46</v>
+      <c r="B24" s="14" t="s">
+        <v>49</v>
       </c>
-      <c r="C24" s="19" t="s">
-        <v>26</v>
+      <c r="C24" s="21" t="s">
+        <v>27</v>
       </c>
-      <c r="D24" s="17"/>
-      <c r="E24" s="12"/>
-      <c r="F24" s="17"/>
-      <c r="G24" s="12" t="s">
-        <v>26</v>
+      <c r="D24" s="23"/>
+      <c r="E24" s="23"/>
+      <c r="F24" s="23"/>
+      <c r="G24" s="22" t="s">
+        <v>27</v>
       </c>
-      <c r="H24" s="16"/>
+      <c r="H24" s="15"/>
       <c r="I24" s="1"/>
       <c r="J24" s="1"/>
       <c r="K24" s="1"/>
@@ -1604,24 +1625,26 @@
       <c r="M24" s="1"/>
     </row>
     <row r="25" spans="1:13" ht="39.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A25" s="18" t="s">
-        <v>51</v>
+      <c r="A25" s="16" t="s">
+        <v>52</v>
       </c>
-      <c r="B25" s="15" t="s">
-        <v>46</v>
+      <c r="B25" s="14" t="s">
+        <v>49</v>
       </c>
-      <c r="C25" s="20" t="s">
-        <v>26</v>
+      <c r="C25" s="21" t="s">
+        <v>27</v>
       </c>
-      <c r="D25" s="12" t="s">
-        <v>26</v>
+      <c r="D25" s="22" t="s">
+        <v>27</v>
       </c>
-      <c r="E25" s="17"/>
-      <c r="F25" s="17"/>
-      <c r="G25" s="12" t="s">
-        <v>26</v>
+      <c r="E25" s="15"/>
+      <c r="F25" s="23"/>
+      <c r="G25" s="22" t="s">
+        <v>27</v>
       </c>
-      <c r="H25" s="16"/>
+      <c r="H25" s="22" t="s">
+        <v>27</v>
+      </c>
       <c r="I25" s="1"/>
       <c r="J25" s="1"/>
       <c r="K25" s="1"/>
@@ -1629,62 +1652,74 @@
       <c r="M25" s="1"/>
     </row>
     <row r="26" spans="1:13" ht="39.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A26" s="18" t="s">
-        <v>52</v>
+      <c r="A26" s="16" t="s">
+        <v>53</v>
       </c>
-      <c r="B26" s="15" t="s">
-        <v>46</v>
+      <c r="B26" s="14" t="s">
+        <v>49</v>
       </c>
-      <c r="C26" s="20"/>
-      <c r="D26" s="17"/>
-      <c r="E26" s="12"/>
-      <c r="F26" s="12"/>
-      <c r="G26" s="16"/>
-      <c r="H26" s="16" t="s">
-        <v>26</v>
+      <c r="C26" s="22" t="s">
+        <v>27</v>
       </c>
+      <c r="D26" s="15"/>
+      <c r="E26" s="24"/>
+      <c r="F26" s="15"/>
+      <c r="G26" s="21" t="s">
+        <v>27</v>
+      </c>
+      <c r="H26" s="23"/>
       <c r="I26" s="1"/>
       <c r="J26" s="1"/>
       <c r="K26" s="1"/>
       <c r="L26" s="1"/>
       <c r="M26" s="1"/>
     </row>
-    <row r="27" spans="1:13" ht="19.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A27" s="33" t="s">
-        <v>53</v>
+    <row r="27" spans="1:13" ht="39.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A27" s="16" t="s">
+        <v>54</v>
       </c>
-      <c r="B27" s="29"/>
-      <c r="C27" s="29"/>
-      <c r="D27" s="29"/>
-      <c r="E27" s="29"/>
-      <c r="F27" s="29"/>
-      <c r="G27" s="29"/>
-      <c r="H27" s="34"/>
+      <c r="B27" s="14" t="s">
+        <v>55</v>
+      </c>
+      <c r="C27" s="22" t="s">
+        <v>27</v>
+      </c>
+      <c r="D27" s="22" t="s">
+        <v>27</v>
+      </c>
+      <c r="E27" s="24"/>
+      <c r="F27" s="15"/>
+      <c r="G27" s="21" t="s">
+        <v>27</v>
+      </c>
+      <c r="H27" s="23"/>
       <c r="I27" s="1"/>
       <c r="J27" s="1"/>
       <c r="K27" s="1"/>
       <c r="L27" s="1"/>
       <c r="M27" s="1"/>
     </row>
-    <row r="28" spans="1:13" ht="43.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A28" s="21" t="s">
-        <v>54</v>
+    <row r="28" spans="1:13" ht="39.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A28" s="28" t="s">
+        <v>56</v>
       </c>
       <c r="B28" s="11" t="s">
-        <v>55</v>
+        <v>49</v>
       </c>
-      <c r="C28" s="16" t="s">
-        <v>26</v>
+      <c r="C28" s="22" t="s">
+        <v>27</v>
       </c>
-      <c r="D28" s="16" t="s">
-        <v>26</v>
+      <c r="D28" s="23"/>
+      <c r="E28" s="24"/>
+      <c r="F28" s="21" t="s">
+        <v>27</v>
       </c>
-      <c r="E28" s="12"/>
-      <c r="F28" s="12"/>
-      <c r="G28" s="16" t="s">
-        <v>26</v>
+      <c r="G28" s="22" t="s">
+        <v>27</v>
       </c>
-      <c r="H28" s="22"/>
+      <c r="H28" s="22" t="s">
+        <v>27</v>
+      </c>
       <c r="I28" s="1"/>
       <c r="J28" s="1"/>
       <c r="K28" s="1"/>
@@ -1692,49 +1727,43 @@
       <c r="M28" s="1"/>
     </row>
     <row r="29" spans="1:13" ht="39.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A29" s="23" t="s">
-        <v>56</v>
+      <c r="A29" s="25" t="s">
+        <v>57</v>
       </c>
-      <c r="B29" s="11" t="s">
-        <v>55</v>
-      </c>
-      <c r="C29" s="12" t="s">
-        <v>26</v>
-      </c>
-      <c r="D29" s="24"/>
-      <c r="E29" s="12"/>
-      <c r="F29" s="16" t="s">
-        <v>26</v>
-      </c>
-      <c r="G29" s="24" t="s">
-        <v>26</v>
-      </c>
-      <c r="H29" s="22"/>
+      <c r="B29" s="26"/>
+      <c r="C29" s="26"/>
+      <c r="D29" s="26"/>
+      <c r="E29" s="26"/>
+      <c r="F29" s="26"/>
+      <c r="G29" s="26"/>
+      <c r="H29" s="27"/>
       <c r="I29" s="1"/>
       <c r="J29" s="1"/>
       <c r="K29" s="1"/>
       <c r="L29" s="1"/>
       <c r="M29" s="1"/>
     </row>
-    <row r="30" spans="1:13" ht="39.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A30" s="23" t="s">
-        <v>57</v>
+    <row r="30" spans="1:13" ht="39.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A30" s="17" t="s">
+        <v>58</v>
       </c>
-      <c r="B30" s="14" t="s">
-        <v>55</v>
+      <c r="B30" s="11" t="s">
+        <v>59</v>
       </c>
-      <c r="C30" s="16" t="s">
-        <v>26</v>
+      <c r="C30" s="22" t="s">
+        <v>27</v>
       </c>
-      <c r="D30" s="12" t="s">
-        <v>26</v>
+      <c r="D30" s="22" t="s">
+        <v>27</v>
       </c>
-      <c r="E30" s="16"/>
-      <c r="F30" s="16"/>
-      <c r="G30" s="12" t="s">
-        <v>26</v>
+      <c r="E30" s="24"/>
+      <c r="F30" s="22" t="s">
+        <v>27</v>
       </c>
-      <c r="H30" s="22"/>
+      <c r="G30" s="22" t="s">
+        <v>27</v>
+      </c>
+      <c r="H30" s="18"/>
       <c r="I30" s="1"/>
       <c r="J30" s="1"/>
       <c r="K30" s="1"/>
@@ -1742,47 +1771,49 @@
       <c r="M30" s="1"/>
     </row>
     <row r="31" spans="1:13" ht="39.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A31" s="23" t="s">
-        <v>58</v>
+      <c r="A31" s="19" t="s">
+        <v>60</v>
       </c>
       <c r="B31" s="11" t="s">
-        <v>55</v>
+        <v>59</v>
       </c>
-      <c r="C31" s="24" t="s">
-        <v>26</v>
+      <c r="C31" s="21" t="s">
+        <v>27</v>
       </c>
-      <c r="D31" s="16"/>
-      <c r="E31" s="12"/>
-      <c r="F31" s="12" t="s">
-        <v>26</v>
+      <c r="D31" s="20"/>
+      <c r="E31" s="24"/>
+      <c r="F31" s="22" t="s">
+        <v>27</v>
       </c>
-      <c r="G31" s="16" t="s">
-        <v>26</v>
+      <c r="G31" s="22" t="s">
+        <v>27</v>
       </c>
-      <c r="H31" s="22"/>
+      <c r="H31" s="18"/>
       <c r="I31" s="1"/>
       <c r="J31" s="1"/>
       <c r="K31" s="1"/>
       <c r="L31" s="1"/>
       <c r="M31" s="1"/>
     </row>
-    <row r="32" spans="1:13" ht="39.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A32" s="23" t="s">
+    <row r="32" spans="1:13" ht="39.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A32" s="19" t="s">
+        <v>61</v>
+      </c>
+      <c r="B32" s="13" t="s">
         <v>59</v>
       </c>
-      <c r="B32" s="11" t="s">
-        <v>55</v>
+      <c r="C32" s="22" t="s">
+        <v>27</v>
       </c>
-      <c r="C32" s="12" t="s">
-        <v>26</v>
+      <c r="D32" s="21" t="s">
+        <v>27</v>
       </c>
-      <c r="D32" s="24"/>
-      <c r="E32" s="12"/>
-      <c r="F32" s="16"/>
-      <c r="G32" s="16" t="s">
-        <v>26</v>
+      <c r="E32" s="23"/>
+      <c r="F32" s="23"/>
+      <c r="G32" s="21" t="s">
+        <v>27</v>
       </c>
-      <c r="H32" s="22"/>
+      <c r="H32" s="18"/>
       <c r="I32" s="1"/>
       <c r="J32" s="1"/>
       <c r="K32" s="1"/>
@@ -1790,67 +1821,107 @@
       <c r="M32" s="1"/>
     </row>
     <row r="33" spans="1:13" ht="39.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A33" s="23" t="s">
-        <v>60</v>
+      <c r="A33" s="19" t="s">
+        <v>62</v>
       </c>
       <c r="B33" s="11" t="s">
-        <v>55</v>
+        <v>59</v>
       </c>
-      <c r="C33" s="16"/>
-      <c r="D33" s="12" t="s">
-        <v>26</v>
+      <c r="C33" s="22" t="s">
+        <v>27</v>
       </c>
+      <c r="D33" s="23"/>
       <c r="E33" s="24"/>
-      <c r="F33" s="24"/>
-      <c r="G33" s="12"/>
-      <c r="H33" s="16" t="s">
-        <v>26</v>
+      <c r="F33" s="22" t="s">
+        <v>27</v>
       </c>
+      <c r="G33" s="22" t="s">
+        <v>27</v>
+      </c>
+      <c r="H33" s="18"/>
       <c r="I33" s="1"/>
       <c r="J33" s="1"/>
       <c r="K33" s="1"/>
       <c r="L33" s="1"/>
       <c r="M33" s="1"/>
     </row>
-    <row r="34" spans="1:13" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A34" s="25"/>
-      <c r="B34" s="26"/>
-      <c r="C34" s="27"/>
-      <c r="D34" s="27"/>
-      <c r="E34" s="27"/>
-      <c r="F34" s="27"/>
-      <c r="G34" s="27"/>
-      <c r="H34" s="27"/>
+    <row r="34" spans="1:13" ht="39.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A34" s="19" t="s">
+        <v>63</v>
+      </c>
+      <c r="B34" s="11" t="s">
+        <v>59</v>
+      </c>
+      <c r="C34" s="22" t="s">
+        <v>27</v>
+      </c>
+      <c r="D34" s="23"/>
+      <c r="E34" s="24"/>
+      <c r="F34" s="22" t="s">
+        <v>27</v>
+      </c>
+      <c r="G34" s="22" t="s">
+        <v>27</v>
+      </c>
+      <c r="H34" s="18"/>
       <c r="I34" s="1"/>
       <c r="J34" s="1"/>
       <c r="K34" s="1"/>
       <c r="L34" s="1"/>
       <c r="M34" s="1"/>
     </row>
-    <row r="35" spans="1:13" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A35" s="2"/>
-      <c r="B35" s="2"/>
-      <c r="C35" s="2"/>
-      <c r="D35" s="2"/>
-      <c r="E35" s="2"/>
-      <c r="F35" s="2"/>
-      <c r="G35" s="2"/>
-      <c r="H35" s="2"/>
+    <row r="35" spans="1:13" ht="39.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A35" s="19" t="s">
+        <v>64</v>
+      </c>
+      <c r="B35" s="11" t="s">
+        <v>59</v>
+      </c>
+      <c r="C35" s="22" t="s">
+        <v>27</v>
+      </c>
+      <c r="D35" s="22" t="s">
+        <v>27</v>
+      </c>
+      <c r="E35" s="24"/>
+      <c r="F35" s="21" t="s">
+        <v>27</v>
+      </c>
+      <c r="G35" s="22" t="s">
+        <v>27</v>
+      </c>
+      <c r="H35" s="22" t="s">
+        <v>27</v>
+      </c>
       <c r="I35" s="1"/>
       <c r="J35" s="1"/>
       <c r="K35" s="1"/>
       <c r="L35" s="1"/>
       <c r="M35" s="1"/>
     </row>
-    <row r="36" spans="1:13" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A36" s="2"/>
-      <c r="B36" s="2"/>
-      <c r="C36" s="2"/>
-      <c r="D36" s="2"/>
-      <c r="E36" s="2"/>
-      <c r="F36" s="2"/>
-      <c r="G36" s="2"/>
-      <c r="H36" s="2"/>
+    <row r="36" spans="1:13" ht="39.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A36" s="19" t="s">
+        <v>65</v>
+      </c>
+      <c r="B36" s="11" t="s">
+        <v>59</v>
+      </c>
+      <c r="C36" s="22" t="s">
+        <v>27</v>
+      </c>
+      <c r="D36" s="23"/>
+      <c r="E36" s="22" t="s">
+        <v>27</v>
+      </c>
+      <c r="F36" s="21" t="s">
+        <v>27</v>
+      </c>
+      <c r="G36" s="22" t="s">
+        <v>27</v>
+      </c>
+      <c r="H36" s="22" t="s">
+        <v>27</v>
+      </c>
       <c r="I36" s="1"/>
       <c r="J36" s="1"/>
       <c r="K36" s="1"/>
@@ -16303,14 +16374,14 @@
       <c r="M999" s="1"/>
     </row>
     <row r="1000" spans="1:13" ht="15" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A1000" s="1"/>
-      <c r="B1000" s="1"/>
-      <c r="C1000" s="1"/>
-      <c r="D1000" s="1"/>
-      <c r="E1000" s="1"/>
-      <c r="F1000" s="1"/>
-      <c r="G1000" s="1"/>
-      <c r="H1000" s="1"/>
+      <c r="A1000" s="2"/>
+      <c r="B1000" s="2"/>
+      <c r="C1000" s="2"/>
+      <c r="D1000" s="2"/>
+      <c r="E1000" s="2"/>
+      <c r="F1000" s="2"/>
+      <c r="G1000" s="2"/>
+      <c r="H1000" s="2"/>
       <c r="I1000" s="1"/>
       <c r="J1000" s="1"/>
       <c r="K1000" s="1"/>
@@ -16318,34 +16389,62 @@
       <c r="M1000" s="1"/>
     </row>
     <row r="1001" spans="1:13" ht="15" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A1001" s="1"/>
-      <c r="B1001" s="1"/>
-      <c r="C1001" s="1"/>
-      <c r="D1001" s="1"/>
-      <c r="E1001" s="1"/>
-      <c r="F1001" s="1"/>
-      <c r="G1001" s="1"/>
-      <c r="H1001" s="1"/>
+      <c r="A1001" s="2"/>
+      <c r="B1001" s="2"/>
+      <c r="C1001" s="2"/>
+      <c r="D1001" s="2"/>
+      <c r="E1001" s="2"/>
+      <c r="F1001" s="2"/>
+      <c r="G1001" s="2"/>
+      <c r="H1001" s="2"/>
       <c r="I1001" s="1"/>
       <c r="J1001" s="1"/>
       <c r="K1001" s="1"/>
       <c r="L1001" s="1"/>
       <c r="M1001" s="1"/>
     </row>
+    <row r="1002" spans="1:13" ht="12.75" x14ac:dyDescent="0.2">
+      <c r="A1002" s="1"/>
+      <c r="B1002" s="1"/>
+      <c r="C1002" s="1"/>
+      <c r="D1002" s="1"/>
+      <c r="E1002" s="1"/>
+      <c r="F1002" s="1"/>
+      <c r="G1002" s="1"/>
+      <c r="H1002" s="1"/>
+      <c r="I1002" s="1"/>
+      <c r="J1002" s="1"/>
+      <c r="K1002" s="1"/>
+      <c r="L1002" s="1"/>
+      <c r="M1002" s="1"/>
+    </row>
+    <row r="1003" spans="1:13" ht="12.75" x14ac:dyDescent="0.2">
+      <c r="A1003" s="1"/>
+      <c r="B1003" s="1"/>
+      <c r="C1003" s="1"/>
+      <c r="D1003" s="1"/>
+      <c r="E1003" s="1"/>
+      <c r="F1003" s="1"/>
+      <c r="G1003" s="1"/>
+      <c r="H1003" s="1"/>
+      <c r="I1003" s="1"/>
+      <c r="J1003" s="1"/>
+      <c r="K1003" s="1"/>
+      <c r="L1003" s="1"/>
+      <c r="M1003" s="1"/>
+    </row>
   </sheetData>
-  <mergeCells count="12">
-    <mergeCell ref="A27:H27"/>
-    <mergeCell ref="F3:H3"/>
+  <mergeCells count="10">
     <mergeCell ref="B6:B7"/>
     <mergeCell ref="A8:H8"/>
     <mergeCell ref="A6:A7"/>
     <mergeCell ref="A3:E3"/>
     <mergeCell ref="A4:E4"/>
     <mergeCell ref="G1:H1"/>
+    <mergeCell ref="A2:H2"/>
     <mergeCell ref="A1:F1"/>
-    <mergeCell ref="A2:H2"/>
-    <mergeCell ref="A19:H19"/>
     <mergeCell ref="A5:H5"/>
+    <mergeCell ref="F3:H3"/>
   </mergeCells>
   <hyperlinks>
     <hyperlink ref="A5" r:id="rId1" display="Adresse URL du portfolio : https://flaimeur.github.io" xr:uid="{00000000-0004-0000-0000-000000000000}"/>

--- a/assets/competences.xlsx
+++ b/assets/competences.xlsx
@@ -5,10 +5,10 @@
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\bobom\Downloads\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\bobom\Desktop\portofio\assets\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D884A3C6-965C-47E2-8261-B9FFD6A25725}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{377A6C0B-E94B-4546-8B56-9254BDD9BE42}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -361,7 +361,7 @@
       </patternFill>
     </fill>
   </fills>
-  <borders count="27">
+  <borders count="2">
     <border>
       <left/>
       <right/>
@@ -370,356 +370,17 @@
       <diagonal/>
     </border>
     <border>
-      <left/>
-      <right/>
-      <top style="medium">
-        <color rgb="FF494429"/>
+      <left style="thin">
+        <color indexed="64"/>
+      </left>
+      <right style="thin">
+        <color indexed="64"/>
+      </right>
+      <top style="thin">
+        <color indexed="64"/>
       </top>
       <bottom style="thin">
-        <color rgb="FF494429"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
-      <right style="thin">
-        <color rgb="FF494429"/>
-      </right>
-      <top style="medium">
-        <color rgb="FF494429"/>
-      </top>
-      <bottom style="thin">
-        <color rgb="FF494429"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
-      <right style="medium">
-        <color rgb="FF494429"/>
-      </right>
-      <top style="medium">
-        <color rgb="FF494429"/>
-      </top>
-      <bottom style="thin">
-        <color rgb="FF494429"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
-      <right/>
-      <top style="thin">
-        <color rgb="FF494429"/>
-      </top>
-      <bottom style="thin">
-        <color rgb="FF494429"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
-      <right style="thin">
-        <color rgb="FF494429"/>
-      </right>
-      <top style="thin">
-        <color rgb="FF494429"/>
-      </top>
-      <bottom style="thin">
-        <color rgb="FF494429"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="thin">
-        <color rgb="FF494429"/>
-      </left>
-      <right/>
-      <top style="thin">
-        <color rgb="FF494429"/>
-      </top>
-      <bottom style="thin">
-        <color rgb="FF494429"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
-      <right style="medium">
-        <color rgb="FF494429"/>
-      </right>
-      <top style="thin">
-        <color rgb="FF494429"/>
-      </top>
-      <bottom style="thin">
-        <color rgb="FF494429"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
-      <right/>
-      <top style="thin">
-        <color rgb="FF494429"/>
-      </top>
-      <bottom style="medium">
-        <color rgb="FF494429"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
-      <right style="medium">
-        <color rgb="FF494429"/>
-      </right>
-      <top style="thin">
-        <color rgb="FF494429"/>
-      </top>
-      <bottom style="medium">
-        <color rgb="FF494429"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="medium">
-        <color rgb="FF494429"/>
-      </left>
-      <right style="thin">
-        <color rgb="FF494429"/>
-      </right>
-      <top style="medium">
-        <color rgb="FF494429"/>
-      </top>
-      <bottom/>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="thin">
-        <color rgb="FF494429"/>
-      </left>
-      <right style="thin">
-        <color rgb="FF494429"/>
-      </right>
-      <top style="medium">
-        <color rgb="FF494429"/>
-      </top>
-      <bottom style="thin">
-        <color rgb="FF494429"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="thin">
-        <color rgb="FF494429"/>
-      </left>
-      <right style="medium">
-        <color rgb="FF494429"/>
-      </right>
-      <top style="medium">
-        <color rgb="FF494429"/>
-      </top>
-      <bottom style="thin">
-        <color rgb="FF494429"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="medium">
-        <color rgb="FF494429"/>
-      </left>
-      <right style="thin">
-        <color rgb="FF494429"/>
-      </right>
-      <top/>
-      <bottom/>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="thin">
-        <color rgb="FF494429"/>
-      </left>
-      <right style="thin">
-        <color rgb="FF494429"/>
-      </right>
-      <top/>
-      <bottom style="medium">
-        <color rgb="FF494429"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="thin">
-        <color rgb="FF494429"/>
-      </left>
-      <right style="thin">
-        <color rgb="FF494429"/>
-      </right>
-      <top style="thin">
-        <color rgb="FF494429"/>
-      </top>
-      <bottom/>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="thin">
-        <color rgb="FF494429"/>
-      </left>
-      <right style="medium">
-        <color rgb="FF494429"/>
-      </right>
-      <top style="thin">
-        <color rgb="FF494429"/>
-      </top>
-      <bottom/>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="medium">
-        <color rgb="FF494429"/>
-      </left>
-      <right style="thin">
-        <color rgb="FF494429"/>
-      </right>
-      <top style="thin">
-        <color rgb="FF494429"/>
-      </top>
-      <bottom style="thin">
-        <color rgb="FF494429"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="thin">
-        <color rgb="FF494429"/>
-      </left>
-      <right style="thin">
-        <color rgb="FF494429"/>
-      </right>
-      <top style="thin">
-        <color rgb="FF494429"/>
-      </top>
-      <bottom style="thin">
-        <color rgb="FF494429"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="thin">
-        <color rgb="FF000000"/>
-      </left>
-      <right style="thin">
-        <color rgb="FF000000"/>
-      </right>
-      <top style="thin">
-        <color rgb="FF000000"/>
-      </top>
-      <bottom style="thin">
-        <color rgb="FF000000"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="medium">
-        <color rgb="FF4A452A"/>
-      </left>
-      <right style="thin">
-        <color rgb="FF4A452A"/>
-      </right>
-      <top style="thin">
-        <color rgb="FF4A452A"/>
-      </top>
-      <bottom style="thin">
-        <color rgb="FF4A452A"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="thin">
-        <color rgb="FF494429"/>
-      </left>
-      <right style="medium">
-        <color rgb="FF494429"/>
-      </right>
-      <top style="thin">
-        <color rgb="FF494429"/>
-      </top>
-      <bottom style="thin">
-        <color rgb="FF494429"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="thin">
-        <color rgb="FF494429"/>
-      </left>
-      <right style="thin">
-        <color rgb="FF494429"/>
-      </right>
-      <top style="medium">
-        <color rgb="FF494429"/>
-      </top>
-      <bottom style="medium">
-        <color rgb="FF494429"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="medium">
-        <color rgb="FF494429"/>
-      </left>
-      <right style="medium">
-        <color rgb="FF494429"/>
-      </right>
-      <top style="medium">
-        <color rgb="FF494429"/>
-      </top>
-      <bottom style="thin">
-        <color rgb="FF494429"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="medium">
-        <color rgb="FF494429"/>
-      </left>
-      <right style="medium">
-        <color rgb="FF494429"/>
-      </right>
-      <top style="thin">
-        <color rgb="FF494429"/>
-      </top>
-      <bottom style="thin">
-        <color rgb="FF494429"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="medium">
-        <color rgb="FF494429"/>
-      </left>
-      <right style="thin">
-        <color rgb="FF494429"/>
-      </right>
-      <top style="medium">
-        <color rgb="FF494429"/>
-      </top>
-      <bottom style="thin">
-        <color rgb="FF494429"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="medium">
-        <color rgb="FF494429"/>
-      </left>
-      <right style="medium">
-        <color rgb="FF494429"/>
-      </right>
-      <top style="thin">
-        <color rgb="FF494429"/>
-      </top>
-      <bottom style="medium">
-        <color rgb="FF494429"/>
+        <color indexed="64"/>
       </bottom>
       <diagonal/>
     </border>
@@ -727,120 +388,86 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="47">
+  <cellXfs count="29">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" textRotation="90" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" textRotation="90" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="11" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="12" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="15" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" textRotation="90" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="16" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" textRotation="90" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="17" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="18" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="18" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="3" borderId="19" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="13" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="1" fontId="11" fillId="3" borderId="20" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="3" borderId="21" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="3" borderId="18" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="2" borderId="19" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="2" borderId="19" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="3" borderId="19" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="4" borderId="19" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="24" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="4" xfId="0" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="7" xfId="0" applyBorder="1"/>
-    <xf numFmtId="1" fontId="12" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="17" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="4" xfId="0" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="5" xfId="0" applyBorder="1"/>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="26" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="8" xfId="0" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="9" xfId="0" applyBorder="1"/>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="12" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="3" xfId="0" applyBorder="1"/>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="22" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" textRotation="90" wrapText="1"/>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="14" xfId="0" applyBorder="1"/>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="23" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    <xf numFmtId="0" fontId="10" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    <xf numFmtId="0" fontId="4" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="13" xfId="0" applyBorder="1"/>
-    <xf numFmtId="0" fontId="14" fillId="0" borderId="25" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
+    <xf numFmtId="0" fontId="4" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyBorder="1"/>
+    <xf numFmtId="1" fontId="11" fillId="3" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="1" fontId="12" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -1069,18 +696,18 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:13" ht="39.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A1" s="32" t="s">
+      <c r="A1" s="3" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="33"/>
-      <c r="C1" s="33"/>
-      <c r="D1" s="33"/>
-      <c r="E1" s="33"/>
-      <c r="F1" s="33"/>
-      <c r="G1" s="32" t="s">
+      <c r="B1" s="4"/>
+      <c r="C1" s="4"/>
+      <c r="D1" s="4"/>
+      <c r="E1" s="4"/>
+      <c r="F1" s="4"/>
+      <c r="G1" s="3" t="s">
         <v>1</v>
       </c>
-      <c r="H1" s="33"/>
+      <c r="H1" s="4"/>
       <c r="I1" s="1"/>
       <c r="J1" s="1"/>
       <c r="K1" s="1"/>
@@ -1088,16 +715,16 @@
       <c r="M1" s="1"/>
     </row>
     <row r="2" spans="1:13" ht="40.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A2" s="32" t="s">
+      <c r="A2" s="3" t="s">
         <v>2</v>
       </c>
-      <c r="B2" s="33"/>
-      <c r="C2" s="33"/>
-      <c r="D2" s="33"/>
-      <c r="E2" s="33"/>
-      <c r="F2" s="33"/>
-      <c r="G2" s="33"/>
-      <c r="H2" s="33"/>
+      <c r="B2" s="4"/>
+      <c r="C2" s="4"/>
+      <c r="D2" s="4"/>
+      <c r="E2" s="4"/>
+      <c r="F2" s="4"/>
+      <c r="G2" s="4"/>
+      <c r="H2" s="4"/>
       <c r="I2" s="1"/>
       <c r="J2" s="1"/>
       <c r="K2" s="1"/>
@@ -1105,18 +732,18 @@
       <c r="M2" s="1"/>
     </row>
     <row r="3" spans="1:13" ht="39.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A3" s="45" t="s">
+      <c r="A3" s="5" t="s">
         <v>3</v>
       </c>
-      <c r="B3" s="38"/>
-      <c r="C3" s="38"/>
-      <c r="D3" s="38"/>
-      <c r="E3" s="46"/>
-      <c r="F3" s="37" t="s">
+      <c r="B3" s="4"/>
+      <c r="C3" s="4"/>
+      <c r="D3" s="4"/>
+      <c r="E3" s="4"/>
+      <c r="F3" s="6" t="s">
         <v>4</v>
       </c>
-      <c r="G3" s="38"/>
-      <c r="H3" s="39"/>
+      <c r="G3" s="4"/>
+      <c r="H3" s="4"/>
       <c r="I3" s="1"/>
       <c r="J3" s="1"/>
       <c r="K3" s="2"/>
@@ -1124,20 +751,20 @@
       <c r="M3" s="2"/>
     </row>
     <row r="4" spans="1:13" ht="39.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A4" s="29" t="s">
+      <c r="A4" s="6" t="s">
         <v>5</v>
       </c>
-      <c r="B4" s="30"/>
-      <c r="C4" s="30"/>
-      <c r="D4" s="30"/>
-      <c r="E4" s="31"/>
-      <c r="F4" s="3" t="s">
+      <c r="B4" s="4"/>
+      <c r="C4" s="4"/>
+      <c r="D4" s="4"/>
+      <c r="E4" s="4"/>
+      <c r="F4" s="7" t="s">
         <v>6</v>
       </c>
-      <c r="G4" s="4" t="s">
+      <c r="G4" s="8" t="s">
         <v>7</v>
       </c>
-      <c r="H4" s="5" t="s">
+      <c r="H4" s="8" t="s">
         <v>8</v>
       </c>
       <c r="I4" s="1"/>
@@ -1147,16 +774,16 @@
       <c r="M4" s="1"/>
     </row>
     <row r="5" spans="1:13" ht="39.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A5" s="34" t="s">
+      <c r="A5" s="9" t="s">
         <v>9</v>
       </c>
-      <c r="B5" s="35"/>
-      <c r="C5" s="35"/>
-      <c r="D5" s="35"/>
-      <c r="E5" s="35"/>
-      <c r="F5" s="35"/>
-      <c r="G5" s="35"/>
-      <c r="H5" s="36"/>
+      <c r="B5" s="4"/>
+      <c r="C5" s="4"/>
+      <c r="D5" s="4"/>
+      <c r="E5" s="4"/>
+      <c r="F5" s="4"/>
+      <c r="G5" s="4"/>
+      <c r="H5" s="4"/>
       <c r="I5" s="1"/>
       <c r="J5" s="1"/>
       <c r="K5" s="1"/>
@@ -1164,28 +791,28 @@
       <c r="M5" s="1"/>
     </row>
     <row r="6" spans="1:13" ht="90" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A6" s="43" t="s">
+      <c r="A6" s="10" t="s">
         <v>10</v>
       </c>
-      <c r="B6" s="40" t="s">
+      <c r="B6" s="11" t="s">
         <v>11</v>
       </c>
-      <c r="C6" s="6" t="s">
+      <c r="C6" s="12" t="s">
         <v>12</v>
       </c>
-      <c r="D6" s="6" t="s">
+      <c r="D6" s="12" t="s">
         <v>13</v>
       </c>
-      <c r="E6" s="6" t="s">
+      <c r="E6" s="12" t="s">
         <v>14</v>
       </c>
-      <c r="F6" s="6" t="s">
+      <c r="F6" s="12" t="s">
         <v>15</v>
       </c>
-      <c r="G6" s="6" t="s">
+      <c r="G6" s="12" t="s">
         <v>16</v>
       </c>
-      <c r="H6" s="7" t="s">
+      <c r="H6" s="12" t="s">
         <v>17</v>
       </c>
       <c r="I6" s="1"/>
@@ -1195,24 +822,24 @@
       <c r="M6" s="1"/>
     </row>
     <row r="7" spans="1:13" ht="324.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A7" s="44"/>
-      <c r="B7" s="41"/>
-      <c r="C7" s="8" t="s">
+      <c r="A7" s="4"/>
+      <c r="B7" s="4"/>
+      <c r="C7" s="13" t="s">
         <v>18</v>
       </c>
-      <c r="D7" s="8" t="s">
+      <c r="D7" s="13" t="s">
         <v>19</v>
       </c>
-      <c r="E7" s="8" t="s">
+      <c r="E7" s="13" t="s">
         <v>20</v>
       </c>
-      <c r="F7" s="8" t="s">
+      <c r="F7" s="13" t="s">
         <v>21</v>
       </c>
-      <c r="G7" s="8" t="s">
+      <c r="G7" s="13" t="s">
         <v>22</v>
       </c>
-      <c r="H7" s="9" t="s">
+      <c r="H7" s="13" t="s">
         <v>23</v>
       </c>
       <c r="I7" s="1"/>
@@ -1222,16 +849,16 @@
       <c r="M7" s="1"/>
     </row>
     <row r="8" spans="1:13" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A8" s="42" t="s">
+      <c r="A8" s="14" t="s">
         <v>24</v>
       </c>
-      <c r="B8" s="38"/>
-      <c r="C8" s="38"/>
-      <c r="D8" s="38"/>
-      <c r="E8" s="38"/>
-      <c r="F8" s="38"/>
-      <c r="G8" s="38"/>
-      <c r="H8" s="39"/>
+      <c r="B8" s="4"/>
+      <c r="C8" s="4"/>
+      <c r="D8" s="4"/>
+      <c r="E8" s="4"/>
+      <c r="F8" s="4"/>
+      <c r="G8" s="4"/>
+      <c r="H8" s="4"/>
       <c r="I8" s="1"/>
       <c r="J8" s="1"/>
       <c r="K8" s="1"/>
@@ -1239,20 +866,20 @@
       <c r="M8" s="1"/>
     </row>
     <row r="9" spans="1:13" ht="39.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A9" s="10" t="s">
+      <c r="A9" s="15" t="s">
         <v>25</v>
       </c>
-      <c r="B9" s="11" t="s">
+      <c r="B9" s="15" t="s">
         <v>26</v>
       </c>
-      <c r="C9" s="21" t="s">
+      <c r="C9" s="16" t="s">
         <v>27</v>
       </c>
-      <c r="D9" s="12"/>
-      <c r="E9" s="12"/>
-      <c r="F9" s="12"/>
-      <c r="G9" s="12"/>
-      <c r="H9" s="22" t="s">
+      <c r="D9" s="17"/>
+      <c r="E9" s="17"/>
+      <c r="F9" s="17"/>
+      <c r="G9" s="17"/>
+      <c r="H9" s="18" t="s">
         <v>27</v>
       </c>
       <c r="I9" s="1"/>
@@ -1262,24 +889,24 @@
       <c r="M9" s="1"/>
     </row>
     <row r="10" spans="1:13" ht="39.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A10" s="10" t="s">
+      <c r="A10" s="15" t="s">
         <v>28</v>
       </c>
-      <c r="B10" s="11" t="s">
+      <c r="B10" s="15" t="s">
         <v>29</v>
       </c>
-      <c r="C10" s="21" t="s">
+      <c r="C10" s="16" t="s">
         <v>27</v>
       </c>
-      <c r="D10" s="21" t="s">
+      <c r="D10" s="16" t="s">
         <v>27</v>
       </c>
-      <c r="E10" s="12"/>
-      <c r="F10" s="12"/>
-      <c r="G10" s="21" t="s">
+      <c r="E10" s="17"/>
+      <c r="F10" s="17"/>
+      <c r="G10" s="16" t="s">
         <v>27</v>
       </c>
-      <c r="H10" s="21" t="s">
+      <c r="H10" s="16" t="s">
         <v>27</v>
       </c>
       <c r="I10" s="1"/>
@@ -1289,24 +916,24 @@
       <c r="M10" s="1"/>
     </row>
     <row r="11" spans="1:13" ht="39.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A11" s="10" t="s">
+      <c r="A11" s="15" t="s">
         <v>30</v>
       </c>
-      <c r="B11" s="11" t="s">
+      <c r="B11" s="15" t="s">
         <v>31</v>
       </c>
-      <c r="C11" s="21" t="s">
+      <c r="C11" s="16" t="s">
         <v>27</v>
       </c>
-      <c r="D11" s="12"/>
-      <c r="E11" s="12"/>
-      <c r="F11" s="22" t="s">
+      <c r="D11" s="17"/>
+      <c r="E11" s="17"/>
+      <c r="F11" s="18" t="s">
         <v>27</v>
       </c>
-      <c r="G11" s="22" t="s">
+      <c r="G11" s="18" t="s">
         <v>27</v>
       </c>
-      <c r="H11" s="21" t="s">
+      <c r="H11" s="16" t="s">
         <v>27</v>
       </c>
       <c r="I11" s="1"/>
@@ -1316,22 +943,22 @@
       <c r="M11" s="1"/>
     </row>
     <row r="12" spans="1:13" ht="39.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A12" s="10" t="s">
+      <c r="A12" s="15" t="s">
         <v>32</v>
       </c>
-      <c r="B12" s="11" t="s">
+      <c r="B12" s="15" t="s">
         <v>33</v>
       </c>
-      <c r="C12" s="21" t="s">
+      <c r="C12" s="16" t="s">
         <v>27</v>
       </c>
-      <c r="D12" s="12"/>
-      <c r="E12" s="12"/>
-      <c r="F12" s="12"/>
-      <c r="G12" s="22" t="s">
+      <c r="D12" s="17"/>
+      <c r="E12" s="17"/>
+      <c r="F12" s="17"/>
+      <c r="G12" s="18" t="s">
         <v>27</v>
       </c>
-      <c r="H12" s="21" t="s">
+      <c r="H12" s="16" t="s">
         <v>27</v>
       </c>
       <c r="I12" s="1"/>
@@ -1341,22 +968,22 @@
       <c r="M12" s="1"/>
     </row>
     <row r="13" spans="1:13" ht="39.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A13" s="10" t="s">
+      <c r="A13" s="15" t="s">
         <v>34</v>
       </c>
-      <c r="B13" s="11" t="s">
+      <c r="B13" s="15" t="s">
         <v>35</v>
       </c>
-      <c r="C13" s="21" t="s">
+      <c r="C13" s="16" t="s">
         <v>27</v>
       </c>
-      <c r="D13" s="12"/>
-      <c r="E13" s="12"/>
-      <c r="F13" s="12"/>
-      <c r="G13" s="22" t="s">
+      <c r="D13" s="17"/>
+      <c r="E13" s="17"/>
+      <c r="F13" s="17"/>
+      <c r="G13" s="18" t="s">
         <v>27</v>
       </c>
-      <c r="H13" s="21" t="s">
+      <c r="H13" s="16" t="s">
         <v>27</v>
       </c>
       <c r="I13" s="1"/>
@@ -1366,24 +993,24 @@
       <c r="M13" s="1"/>
     </row>
     <row r="14" spans="1:13" ht="39.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A14" s="10" t="s">
+      <c r="A14" s="15" t="s">
         <v>36</v>
       </c>
-      <c r="B14" s="11" t="s">
+      <c r="B14" s="15" t="s">
         <v>37</v>
       </c>
-      <c r="C14" s="21" t="s">
+      <c r="C14" s="16" t="s">
         <v>27</v>
       </c>
-      <c r="D14" s="12"/>
-      <c r="E14" s="12"/>
-      <c r="F14" s="22" t="s">
+      <c r="D14" s="17"/>
+      <c r="E14" s="17"/>
+      <c r="F14" s="18" t="s">
         <v>27</v>
       </c>
-      <c r="G14" s="21" t="s">
+      <c r="G14" s="16" t="s">
         <v>27</v>
       </c>
-      <c r="H14" s="21" t="s">
+      <c r="H14" s="16" t="s">
         <v>27</v>
       </c>
       <c r="I14" s="1"/>
@@ -1393,22 +1020,22 @@
       <c r="M14" s="1"/>
     </row>
     <row r="15" spans="1:13" ht="39.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A15" s="10" t="s">
+      <c r="A15" s="15" t="s">
         <v>38</v>
       </c>
-      <c r="B15" s="11" t="s">
+      <c r="B15" s="15" t="s">
         <v>31</v>
       </c>
-      <c r="C15" s="21" t="s">
+      <c r="C15" s="16" t="s">
         <v>27</v>
       </c>
-      <c r="D15" s="12"/>
-      <c r="E15" s="12"/>
-      <c r="F15" s="12"/>
-      <c r="G15" s="22" t="s">
+      <c r="D15" s="17"/>
+      <c r="E15" s="17"/>
+      <c r="F15" s="17"/>
+      <c r="G15" s="18" t="s">
         <v>27</v>
       </c>
-      <c r="H15" s="21" t="s">
+      <c r="H15" s="16" t="s">
         <v>27</v>
       </c>
       <c r="I15" s="1"/>
@@ -1418,26 +1045,26 @@
       <c r="M15" s="1"/>
     </row>
     <row r="16" spans="1:13" ht="39.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A16" s="10" t="s">
+      <c r="A16" s="15" t="s">
         <v>39</v>
       </c>
-      <c r="B16" s="11" t="s">
+      <c r="B16" s="15" t="s">
         <v>40</v>
       </c>
-      <c r="C16" s="21" t="s">
+      <c r="C16" s="16" t="s">
         <v>27</v>
       </c>
-      <c r="D16" s="21" t="s">
+      <c r="D16" s="16" t="s">
         <v>27</v>
       </c>
-      <c r="E16" s="12"/>
-      <c r="F16" s="21" t="s">
+      <c r="E16" s="17"/>
+      <c r="F16" s="16" t="s">
         <v>27</v>
       </c>
-      <c r="G16" s="21" t="s">
+      <c r="G16" s="16" t="s">
         <v>27</v>
       </c>
-      <c r="H16" s="21" t="s">
+      <c r="H16" s="16" t="s">
         <v>27</v>
       </c>
       <c r="I16" s="1"/>
@@ -1447,22 +1074,22 @@
       <c r="M16" s="1"/>
     </row>
     <row r="17" spans="1:13" ht="39.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A17" s="10" t="s">
+      <c r="A17" s="15" t="s">
         <v>41</v>
       </c>
-      <c r="B17" s="11" t="s">
+      <c r="B17" s="15" t="s">
         <v>42</v>
       </c>
-      <c r="C17" s="21" t="s">
+      <c r="C17" s="16" t="s">
         <v>27</v>
       </c>
-      <c r="D17" s="12"/>
-      <c r="E17" s="12"/>
-      <c r="F17" s="12"/>
-      <c r="G17" s="21" t="s">
+      <c r="D17" s="17"/>
+      <c r="E17" s="17"/>
+      <c r="F17" s="17"/>
+      <c r="G17" s="16" t="s">
         <v>27</v>
       </c>
-      <c r="H17" s="21" t="s">
+      <c r="H17" s="16" t="s">
         <v>27</v>
       </c>
       <c r="I17" s="1"/>
@@ -1472,64 +1099,64 @@
       <c r="M17" s="1"/>
     </row>
     <row r="18" spans="1:13" ht="39.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A18" s="10" t="s">
+      <c r="A18" s="15" t="s">
         <v>43</v>
       </c>
-      <c r="B18" s="11" t="s">
+      <c r="B18" s="15" t="s">
         <v>31</v>
       </c>
-      <c r="C18" s="21" t="s">
+      <c r="C18" s="16" t="s">
         <v>27</v>
       </c>
-      <c r="D18" s="12"/>
-      <c r="E18" s="12"/>
-      <c r="F18" s="12"/>
-      <c r="G18" s="21" t="s">
+      <c r="D18" s="17"/>
+      <c r="E18" s="17"/>
+      <c r="F18" s="17"/>
+      <c r="G18" s="16" t="s">
         <v>27</v>
       </c>
-      <c r="H18" s="21" t="s">
+      <c r="H18" s="16" t="s">
         <v>27</v>
       </c>
     </row>
     <row r="19" spans="1:13" ht="39.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A19" s="10" t="s">
+      <c r="A19" s="15" t="s">
         <v>44</v>
       </c>
-      <c r="B19" s="11" t="s">
+      <c r="B19" s="15" t="s">
         <v>31</v>
       </c>
-      <c r="C19" s="21" t="s">
+      <c r="C19" s="16" t="s">
         <v>27</v>
       </c>
-      <c r="D19" s="12"/>
-      <c r="E19" s="12"/>
-      <c r="F19" s="12"/>
-      <c r="G19" s="21" t="s">
+      <c r="D19" s="17"/>
+      <c r="E19" s="17"/>
+      <c r="F19" s="17"/>
+      <c r="G19" s="16" t="s">
         <v>27</v>
       </c>
-      <c r="H19" s="21" t="s">
+      <c r="H19" s="16" t="s">
         <v>27</v>
       </c>
     </row>
     <row r="20" spans="1:13" ht="39.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A20" s="10" t="s">
+      <c r="A20" s="15" t="s">
         <v>45</v>
       </c>
-      <c r="B20" s="11" t="s">
+      <c r="B20" s="15" t="s">
         <v>46</v>
       </c>
-      <c r="C20" s="21" t="s">
+      <c r="C20" s="16" t="s">
         <v>27</v>
       </c>
-      <c r="D20" s="12"/>
-      <c r="E20" s="21" t="s">
+      <c r="D20" s="17"/>
+      <c r="E20" s="16" t="s">
         <v>27</v>
       </c>
-      <c r="F20" s="12"/>
-      <c r="G20" s="21" t="s">
+      <c r="F20" s="17"/>
+      <c r="G20" s="16" t="s">
         <v>27</v>
       </c>
-      <c r="H20" s="21" t="s">
+      <c r="H20" s="16" t="s">
         <v>27</v>
       </c>
       <c r="I20" s="1"/>
@@ -1539,16 +1166,16 @@
       <c r="M20" s="1"/>
     </row>
     <row r="21" spans="1:13" ht="39.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A21" s="25" t="s">
+      <c r="A21" s="19" t="s">
         <v>47</v>
       </c>
-      <c r="B21" s="26"/>
-      <c r="C21" s="26"/>
-      <c r="D21" s="26"/>
-      <c r="E21" s="26"/>
-      <c r="F21" s="26"/>
-      <c r="G21" s="26"/>
-      <c r="H21" s="27"/>
+      <c r="B21" s="20"/>
+      <c r="C21" s="20"/>
+      <c r="D21" s="20"/>
+      <c r="E21" s="20"/>
+      <c r="F21" s="20"/>
+      <c r="G21" s="20"/>
+      <c r="H21" s="20"/>
       <c r="I21" s="1"/>
       <c r="J21" s="1"/>
       <c r="K21" s="1"/>
@@ -1556,22 +1183,22 @@
       <c r="M21" s="1"/>
     </row>
     <row r="22" spans="1:13" ht="39.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A22" s="13" t="s">
+      <c r="A22" s="21" t="s">
         <v>48</v>
       </c>
-      <c r="B22" s="14" t="s">
+      <c r="B22" s="15" t="s">
         <v>49</v>
       </c>
-      <c r="C22" s="21" t="s">
+      <c r="C22" s="16" t="s">
         <v>27</v>
       </c>
-      <c r="D22" s="22" t="s">
+      <c r="D22" s="18" t="s">
         <v>27</v>
       </c>
-      <c r="E22" s="15"/>
+      <c r="E22" s="22"/>
       <c r="F22" s="23"/>
       <c r="G22" s="23"/>
-      <c r="H22" s="15"/>
+      <c r="H22" s="22"/>
       <c r="I22" s="1"/>
       <c r="J22" s="1"/>
       <c r="K22" s="1"/>
@@ -1579,20 +1206,20 @@
       <c r="M22" s="1"/>
     </row>
     <row r="23" spans="1:13" ht="39.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A23" s="13" t="s">
+      <c r="A23" s="21" t="s">
         <v>50</v>
       </c>
-      <c r="B23" s="14" t="s">
+      <c r="B23" s="15" t="s">
         <v>49</v>
       </c>
       <c r="C23" s="24"/>
-      <c r="D23" s="22" t="s">
+      <c r="D23" s="18" t="s">
         <v>27</v>
       </c>
       <c r="E23" s="23"/>
       <c r="F23" s="23"/>
       <c r="G23" s="23"/>
-      <c r="H23" s="21" t="s">
+      <c r="H23" s="16" t="s">
         <v>27</v>
       </c>
       <c r="I23" s="1"/>
@@ -1602,22 +1229,22 @@
       <c r="M23" s="1"/>
     </row>
     <row r="24" spans="1:13" ht="39.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A24" s="13" t="s">
+      <c r="A24" s="21" t="s">
         <v>51</v>
       </c>
-      <c r="B24" s="14" t="s">
+      <c r="B24" s="15" t="s">
         <v>49</v>
       </c>
-      <c r="C24" s="21" t="s">
+      <c r="C24" s="16" t="s">
         <v>27</v>
       </c>
       <c r="D24" s="23"/>
       <c r="E24" s="23"/>
       <c r="F24" s="23"/>
-      <c r="G24" s="22" t="s">
+      <c r="G24" s="18" t="s">
         <v>27</v>
       </c>
-      <c r="H24" s="15"/>
+      <c r="H24" s="22"/>
       <c r="I24" s="1"/>
       <c r="J24" s="1"/>
       <c r="K24" s="1"/>
@@ -1625,24 +1252,24 @@
       <c r="M24" s="1"/>
     </row>
     <row r="25" spans="1:13" ht="39.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A25" s="16" t="s">
+      <c r="A25" s="25" t="s">
         <v>52</v>
       </c>
-      <c r="B25" s="14" t="s">
+      <c r="B25" s="15" t="s">
         <v>49</v>
       </c>
-      <c r="C25" s="21" t="s">
+      <c r="C25" s="16" t="s">
         <v>27</v>
       </c>
-      <c r="D25" s="22" t="s">
+      <c r="D25" s="18" t="s">
         <v>27</v>
       </c>
-      <c r="E25" s="15"/>
+      <c r="E25" s="22"/>
       <c r="F25" s="23"/>
-      <c r="G25" s="22" t="s">
+      <c r="G25" s="18" t="s">
         <v>27</v>
       </c>
-      <c r="H25" s="22" t="s">
+      <c r="H25" s="18" t="s">
         <v>27</v>
       </c>
       <c r="I25" s="1"/>
@@ -1652,19 +1279,19 @@
       <c r="M25" s="1"/>
     </row>
     <row r="26" spans="1:13" ht="39.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A26" s="16" t="s">
+      <c r="A26" s="25" t="s">
         <v>53</v>
       </c>
-      <c r="B26" s="14" t="s">
+      <c r="B26" s="15" t="s">
         <v>49</v>
       </c>
-      <c r="C26" s="22" t="s">
+      <c r="C26" s="18" t="s">
         <v>27</v>
       </c>
-      <c r="D26" s="15"/>
+      <c r="D26" s="22"/>
       <c r="E26" s="24"/>
-      <c r="F26" s="15"/>
-      <c r="G26" s="21" t="s">
+      <c r="F26" s="22"/>
+      <c r="G26" s="16" t="s">
         <v>27</v>
       </c>
       <c r="H26" s="23"/>
@@ -1675,21 +1302,21 @@
       <c r="M26" s="1"/>
     </row>
     <row r="27" spans="1:13" ht="39.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A27" s="16" t="s">
+      <c r="A27" s="25" t="s">
         <v>54</v>
       </c>
-      <c r="B27" s="14" t="s">
+      <c r="B27" s="15" t="s">
         <v>55</v>
       </c>
-      <c r="C27" s="22" t="s">
+      <c r="C27" s="18" t="s">
         <v>27</v>
       </c>
-      <c r="D27" s="22" t="s">
+      <c r="D27" s="18" t="s">
         <v>27</v>
       </c>
       <c r="E27" s="24"/>
-      <c r="F27" s="15"/>
-      <c r="G27" s="21" t="s">
+      <c r="F27" s="22"/>
+      <c r="G27" s="16" t="s">
         <v>27</v>
       </c>
       <c r="H27" s="23"/>
@@ -1700,24 +1327,24 @@
       <c r="M27" s="1"/>
     </row>
     <row r="28" spans="1:13" ht="39.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A28" s="28" t="s">
+      <c r="A28" s="26" t="s">
         <v>56</v>
       </c>
-      <c r="B28" s="11" t="s">
+      <c r="B28" s="15" t="s">
         <v>49</v>
       </c>
-      <c r="C28" s="22" t="s">
+      <c r="C28" s="18" t="s">
         <v>27</v>
       </c>
       <c r="D28" s="23"/>
       <c r="E28" s="24"/>
-      <c r="F28" s="21" t="s">
+      <c r="F28" s="16" t="s">
         <v>27</v>
       </c>
-      <c r="G28" s="22" t="s">
+      <c r="G28" s="18" t="s">
         <v>27</v>
       </c>
-      <c r="H28" s="22" t="s">
+      <c r="H28" s="18" t="s">
         <v>27</v>
       </c>
       <c r="I28" s="1"/>
@@ -1727,16 +1354,16 @@
       <c r="M28" s="1"/>
     </row>
     <row r="29" spans="1:13" ht="39.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A29" s="25" t="s">
+      <c r="A29" s="19" t="s">
         <v>57</v>
       </c>
-      <c r="B29" s="26"/>
-      <c r="C29" s="26"/>
-      <c r="D29" s="26"/>
-      <c r="E29" s="26"/>
-      <c r="F29" s="26"/>
-      <c r="G29" s="26"/>
-      <c r="H29" s="27"/>
+      <c r="B29" s="20"/>
+      <c r="C29" s="20"/>
+      <c r="D29" s="20"/>
+      <c r="E29" s="20"/>
+      <c r="F29" s="20"/>
+      <c r="G29" s="20"/>
+      <c r="H29" s="20"/>
       <c r="I29" s="1"/>
       <c r="J29" s="1"/>
       <c r="K29" s="1"/>
@@ -1744,26 +1371,26 @@
       <c r="M29" s="1"/>
     </row>
     <row r="30" spans="1:13" ht="39.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A30" s="17" t="s">
+      <c r="A30" s="27" t="s">
         <v>58</v>
       </c>
-      <c r="B30" s="11" t="s">
+      <c r="B30" s="15" t="s">
         <v>59</v>
       </c>
-      <c r="C30" s="22" t="s">
+      <c r="C30" s="18" t="s">
         <v>27</v>
       </c>
-      <c r="D30" s="22" t="s">
+      <c r="D30" s="18" t="s">
         <v>27</v>
       </c>
       <c r="E30" s="24"/>
-      <c r="F30" s="22" t="s">
+      <c r="F30" s="18" t="s">
         <v>27</v>
       </c>
-      <c r="G30" s="22" t="s">
+      <c r="G30" s="18" t="s">
         <v>27</v>
       </c>
-      <c r="H30" s="18"/>
+      <c r="H30" s="22"/>
       <c r="I30" s="1"/>
       <c r="J30" s="1"/>
       <c r="K30" s="1"/>
@@ -1771,24 +1398,24 @@
       <c r="M30" s="1"/>
     </row>
     <row r="31" spans="1:13" ht="39.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A31" s="19" t="s">
+      <c r="A31" s="28" t="s">
         <v>60</v>
       </c>
-      <c r="B31" s="11" t="s">
+      <c r="B31" s="15" t="s">
         <v>59</v>
       </c>
-      <c r="C31" s="21" t="s">
+      <c r="C31" s="16" t="s">
         <v>27</v>
       </c>
-      <c r="D31" s="20"/>
+      <c r="D31" s="22"/>
       <c r="E31" s="24"/>
-      <c r="F31" s="22" t="s">
+      <c r="F31" s="18" t="s">
         <v>27</v>
       </c>
-      <c r="G31" s="22" t="s">
+      <c r="G31" s="18" t="s">
         <v>27</v>
       </c>
-      <c r="H31" s="18"/>
+      <c r="H31" s="22"/>
       <c r="I31" s="1"/>
       <c r="J31" s="1"/>
       <c r="K31" s="1"/>
@@ -1796,24 +1423,24 @@
       <c r="M31" s="1"/>
     </row>
     <row r="32" spans="1:13" ht="39.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A32" s="19" t="s">
+      <c r="A32" s="28" t="s">
         <v>61</v>
       </c>
-      <c r="B32" s="13" t="s">
+      <c r="B32" s="21" t="s">
         <v>59</v>
       </c>
-      <c r="C32" s="22" t="s">
+      <c r="C32" s="18" t="s">
         <v>27</v>
       </c>
-      <c r="D32" s="21" t="s">
+      <c r="D32" s="16" t="s">
         <v>27</v>
       </c>
       <c r="E32" s="23"/>
       <c r="F32" s="23"/>
-      <c r="G32" s="21" t="s">
+      <c r="G32" s="16" t="s">
         <v>27</v>
       </c>
-      <c r="H32" s="18"/>
+      <c r="H32" s="22"/>
       <c r="I32" s="1"/>
       <c r="J32" s="1"/>
       <c r="K32" s="1"/>
@@ -1821,24 +1448,24 @@
       <c r="M32" s="1"/>
     </row>
     <row r="33" spans="1:13" ht="39.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A33" s="19" t="s">
+      <c r="A33" s="28" t="s">
         <v>62</v>
       </c>
-      <c r="B33" s="11" t="s">
+      <c r="B33" s="15" t="s">
         <v>59</v>
       </c>
-      <c r="C33" s="22" t="s">
+      <c r="C33" s="18" t="s">
         <v>27</v>
       </c>
       <c r="D33" s="23"/>
       <c r="E33" s="24"/>
-      <c r="F33" s="22" t="s">
+      <c r="F33" s="18" t="s">
         <v>27</v>
       </c>
-      <c r="G33" s="22" t="s">
+      <c r="G33" s="18" t="s">
         <v>27</v>
       </c>
-      <c r="H33" s="18"/>
+      <c r="H33" s="22"/>
       <c r="I33" s="1"/>
       <c r="J33" s="1"/>
       <c r="K33" s="1"/>
@@ -1846,24 +1473,24 @@
       <c r="M33" s="1"/>
     </row>
     <row r="34" spans="1:13" ht="39.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A34" s="19" t="s">
+      <c r="A34" s="28" t="s">
         <v>63</v>
       </c>
-      <c r="B34" s="11" t="s">
+      <c r="B34" s="15" t="s">
         <v>59</v>
       </c>
-      <c r="C34" s="22" t="s">
+      <c r="C34" s="18" t="s">
         <v>27</v>
       </c>
       <c r="D34" s="23"/>
       <c r="E34" s="24"/>
-      <c r="F34" s="22" t="s">
+      <c r="F34" s="18" t="s">
         <v>27</v>
       </c>
-      <c r="G34" s="22" t="s">
+      <c r="G34" s="18" t="s">
         <v>27</v>
       </c>
-      <c r="H34" s="18"/>
+      <c r="H34" s="22"/>
       <c r="I34" s="1"/>
       <c r="J34" s="1"/>
       <c r="K34" s="1"/>
@@ -1871,26 +1498,26 @@
       <c r="M34" s="1"/>
     </row>
     <row r="35" spans="1:13" ht="39.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A35" s="19" t="s">
+      <c r="A35" s="28" t="s">
         <v>64</v>
       </c>
-      <c r="B35" s="11" t="s">
+      <c r="B35" s="15" t="s">
         <v>59</v>
       </c>
-      <c r="C35" s="22" t="s">
+      <c r="C35" s="18" t="s">
         <v>27</v>
       </c>
-      <c r="D35" s="22" t="s">
+      <c r="D35" s="18" t="s">
         <v>27</v>
       </c>
       <c r="E35" s="24"/>
-      <c r="F35" s="21" t="s">
+      <c r="F35" s="16" t="s">
         <v>27</v>
       </c>
-      <c r="G35" s="22" t="s">
+      <c r="G35" s="18" t="s">
         <v>27</v>
       </c>
-      <c r="H35" s="22" t="s">
+      <c r="H35" s="18" t="s">
         <v>27</v>
       </c>
       <c r="I35" s="1"/>
@@ -1900,26 +1527,26 @@
       <c r="M35" s="1"/>
     </row>
     <row r="36" spans="1:13" ht="39.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A36" s="19" t="s">
+      <c r="A36" s="28" t="s">
         <v>65</v>
       </c>
-      <c r="B36" s="11" t="s">
+      <c r="B36" s="15" t="s">
         <v>59</v>
       </c>
-      <c r="C36" s="22" t="s">
+      <c r="C36" s="18" t="s">
         <v>27</v>
       </c>
       <c r="D36" s="23"/>
-      <c r="E36" s="22" t="s">
+      <c r="E36" s="18" t="s">
         <v>27</v>
       </c>
-      <c r="F36" s="21" t="s">
+      <c r="F36" s="16" t="s">
         <v>27</v>
       </c>
-      <c r="G36" s="22" t="s">
+      <c r="G36" s="18" t="s">
         <v>27</v>
       </c>
-      <c r="H36" s="22" t="s">
+      <c r="H36" s="18" t="s">
         <v>27</v>
       </c>
       <c r="I36" s="1"/>
@@ -16435,22 +16062,22 @@
     </row>
   </sheetData>
   <mergeCells count="10">
+    <mergeCell ref="G1:H1"/>
+    <mergeCell ref="A2:H2"/>
+    <mergeCell ref="A1:F1"/>
+    <mergeCell ref="A5:H5"/>
+    <mergeCell ref="F3:H3"/>
     <mergeCell ref="B6:B7"/>
     <mergeCell ref="A8:H8"/>
     <mergeCell ref="A6:A7"/>
     <mergeCell ref="A3:E3"/>
     <mergeCell ref="A4:E4"/>
-    <mergeCell ref="G1:H1"/>
-    <mergeCell ref="A2:H2"/>
-    <mergeCell ref="A1:F1"/>
-    <mergeCell ref="A5:H5"/>
-    <mergeCell ref="F3:H3"/>
   </mergeCells>
   <hyperlinks>
     <hyperlink ref="A5" r:id="rId1" display="Adresse URL du portfolio : https://flaimeur.github.io" xr:uid="{00000000-0004-0000-0000-000000000000}"/>
   </hyperlinks>
   <printOptions horizontalCentered="1" verticalCentered="1"/>
   <pageMargins left="0.19685039370078741" right="0.19685039370078741" top="0.19685039370078741" bottom="0.19685039370078741" header="0" footer="0"/>
-  <pageSetup paperSize="9" orientation="portrait"/>
+  <pageSetup paperSize="9" scale="48" orientation="portrait" r:id="rId2"/>
 </worksheet>
 </file>